--- a/data/raw/gob_sedeco.xlsx
+++ b/data/raw/gob_sedeco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edward\Desktop\Bancomext\Estatales\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_edobru\Desktop\Bancomext\Estatales\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B1437E-AC74-46D2-B520-BD6418279121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71A625D-16CA-42A9-BDDB-53028732912E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9208604F-8F98-4CC8-9CB0-686404284E31}"/>
+    <workbookView xWindow="-28920" yWindow="-7230" windowWidth="29040" windowHeight="15720" xr2:uid="{9208604F-8F98-4CC8-9CB0-686404284E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista GOB-SEDECO" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -284,9 +287,6 @@
     <t xml:space="preserve">Jesús Salvador González Martínez </t>
   </si>
   <si>
-    <t>Rubén Rocha Moya</t>
-  </si>
-  <si>
     <t>Feliciano Castro Meléndrez</t>
   </si>
   <si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>Gobernador/a</t>
+  </si>
+  <si>
+    <t>Yeraldine Bonilla Valverde</t>
   </si>
 </sst>
 </file>
@@ -474,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -483,6 +486,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -818,30 +822,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE4B58-604C-4B66-8B99-04D784DD3D9E}">
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -852,10 +856,10 @@
         <v>37</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -866,10 +870,10 @@
         <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -880,10 +884,10 @@
         <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,10 +898,10 @@
         <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -908,10 +912,10 @@
         <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,10 +926,10 @@
         <v>44</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -936,10 +940,10 @@
         <v>47</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -950,10 +954,10 @@
         <v>49</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,10 +968,10 @@
         <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -978,10 +982,10 @@
         <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -992,10 +996,10 @@
         <v>55</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -1006,10 +1010,10 @@
         <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -1020,10 +1024,10 @@
         <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -1034,10 +1038,10 @@
         <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1048,10 +1052,10 @@
         <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1062,10 +1066,10 @@
         <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1076,10 +1080,10 @@
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1090,10 +1094,10 @@
         <v>69</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -1104,10 +1108,10 @@
         <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
@@ -1118,10 +1122,10 @@
         <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
@@ -1132,10 +1136,10 @@
         <v>75</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1146,10 +1150,10 @@
         <v>77</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -1160,10 +1164,11 @@
         <v>79</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -1174,119 +1179,119 @@
         <v>81</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
